--- a/dados/excel/secretaria_percentis.xlsx
+++ b/dados/excel/secretaria_percentis.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -891,28 +891,28 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>6134.01</v>
+        <v>6101.01</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>3089.25</v>
+        <v>3145.93</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>3762.98</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>4879.19</v>
+        <v>4858.19</v>
       </c>
       <c r="G2" s="10" t="n">
         <v>6422.45</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>10216.99</v>
+        <v>9218.959999999999</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>20309.38</v>
+        <v>20418.89</v>
       </c>
     </row>
     <row r="3">
@@ -922,28 +922,28 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>9384.42</v>
+        <v>9177.84</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>4381.26</v>
+        <v>4353.73</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>6019.67</v>
+        <v>5424.14</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>8339.610000000001</v>
+        <v>8379.790000000001</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>11674.58</v>
+        <v>11756.19</v>
       </c>
       <c r="H3" s="13" t="n">
-        <v>15480.31</v>
+        <v>15452.79</v>
       </c>
       <c r="I3" s="13" t="n">
-        <v>31241.35</v>
+        <v>29761.66</v>
       </c>
     </row>
     <row r="4">
@@ -953,28 +953,28 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>8116</v>
+        <v>8653</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6964.86</v>
+        <v>6936.26</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>932</v>
+        <v>1304.8</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>1975.84</v>
+        <v>2796</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4791.61</v>
+        <v>4876.53</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>10899.13</v>
+        <v>10410.07</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>14964.32</v>
+        <v>14851.41</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>25838.87</v>
+        <v>26199.58</v>
       </c>
     </row>
     <row r="5">
@@ -987,25 +987,25 @@
         <v>164</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>12768.04</v>
+        <v>14380.78</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>4449.86</v>
+        <v>6471.17</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>5348.48</v>
+        <v>7890.09</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>10039.28</v>
+        <v>11847.59</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>18203</v>
+        <v>19464.6</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>24009.79</v>
+        <v>26458.03</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>34160.11</v>
+        <v>32997.38</v>
       </c>
     </row>
     <row r="6">
@@ -1018,25 +1018,25 @@
         <v>37</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>11743.76</v>
+        <v>11467.48</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>4449.86</v>
+        <v>4422.34</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>5945.78</v>
+        <v>5972.48</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>11807.57</v>
+        <v>10220.8</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>14092.07</v>
+        <v>14870.83</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>18732.58</v>
+        <v>20920.86</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>24841.37</v>
+        <v>25224.89</v>
       </c>
     </row>
     <row r="7">
@@ -1046,28 +1046,28 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>2865</v>
+        <v>2861</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>11144.91</v>
+        <v>11100.59</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>4489.06</v>
+        <v>4422.34</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>5545.07</v>
+        <v>5645.9</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>7944.16</v>
+        <v>7997.34</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>13896.1</v>
+        <v>14004.61</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>21929.07</v>
+        <v>22007.37</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>43795.23</v>
+        <v>42117.06</v>
       </c>
     </row>
     <row r="8">
@@ -1077,28 +1077,28 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>9392.120000000001</v>
+        <v>9910.299999999999</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>4711.38</v>
+        <v>4802.83</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7123.76</v>
+        <v>8139.34</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>12178.18</v>
+        <v>12243.57</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>15972.46</v>
+        <v>16529.15</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>45444.19</v>
+        <v>38483</v>
       </c>
     </row>
     <row r="9">
@@ -1108,28 +1108,28 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>18247.87</v>
+        <v>18243.18</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>1084.8</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>4614.97</v>
+        <v>5313.15</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>10437.59</v>
+        <v>11435.39</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>29828.88</v>
+        <v>30260.23</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>46291.62</v>
+        <v>44700.16</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>76228.36</v>
+        <v>70231.69</v>
       </c>
     </row>
     <row r="10">
@@ -1139,28 +1139,28 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>10940.98</v>
+        <v>11918.63</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>5743.46</v>
+        <v>6245.37</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>12261.82</v>
+        <v>12311.61</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>15480.31</v>
+        <v>16358.95</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>17988.25</v>
+        <v>19323.16</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>20031.31</v>
+        <v>22875.84</v>
       </c>
     </row>
     <row r="11">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>7292.56</v>
+        <v>7291.01</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>1084.8</v>
@@ -1182,16 +1182,16 @@
         <v>1084.8</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>5013.68</v>
+        <v>5621.54</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>9501.09</v>
+        <v>10264.51</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>15480.31</v>
+        <v>15135.69</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>23945.92</v>
+        <v>23327.04</v>
       </c>
     </row>
     <row r="12">
@@ -1201,28 +1201,28 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>9551.1</v>
+        <v>9196.35</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>4856.15</v>
+        <v>4883.53</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7568.79</v>
+        <v>7627.65</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>12668.73</v>
+        <v>12641.21</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>18384.57</v>
+        <v>16737.57</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>25273.41</v>
+        <v>23998.74</v>
       </c>
     </row>
     <row r="13">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>9956.200000000001</v>
+        <v>10317.74</v>
       </c>
       <c r="D13" s="13" t="n">
         <v>1084.8</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>4167.35</v>
+        <v>3625.29</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>8129.64</v>
+        <v>7917.37</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>12946.89</v>
+        <v>14801.61</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>19846.3</v>
+        <v>20513.77</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>37504.82</v>
+        <v>47727.2</v>
       </c>
     </row>
     <row r="14">
@@ -1263,28 +1263,28 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>12422.22</v>
+        <v>13057.73</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>4638.59</v>
+        <v>5254.54</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>12100.38</v>
+        <v>13283.72</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>15963.28</v>
+        <v>15935.77</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>22497.08</v>
+        <v>22875.84</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>43441.64</v>
+        <v>47773.99</v>
       </c>
     </row>
     <row r="15">
@@ -1297,25 +1297,25 @@
         <v>73</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>8134.96</v>
+        <v>8103.6</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>1084.8</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>4449.86</v>
+        <v>4422.33</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>5734.34</v>
+        <v>5309.11</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>12211.99</v>
+        <v>12184.47</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>15480.31</v>
+        <v>15452.79</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>22082.93</v>
+        <v>22055.41</v>
       </c>
     </row>
     <row r="16">
@@ -1328,25 +1328,25 @@
         <v>55</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>10137.32</v>
+        <v>10936.47</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>6143.7</v>
+        <v>5273.18</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>9457.52</v>
+        <v>10410.07</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>14165.75</v>
+        <v>14781.23</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>16740.72</v>
+        <v>17177.54</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>24418.87</v>
+        <v>30645.58</v>
       </c>
     </row>
     <row r="17">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>9396.02</v>
+        <v>9589.709999999999</v>
       </c>
       <c r="D17" s="13" t="n">
         <v>1084.8</v>
@@ -1368,16 +1368,16 @@
         <v>5517.65</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>7717.44</v>
+        <v>7750.08</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>12685.37</v>
+        <v>12416.95</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>16514.02</v>
+        <v>16310.17</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>32330.33</v>
+        <v>34460.65</v>
       </c>
     </row>
     <row r="18">
@@ -1390,25 +1390,25 @@
         <v>129</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>10132.91</v>
+        <v>9844.42</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3195.31</v>
+        <v>2849.59</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>5242.68</v>
+        <v>5212.8</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>8546</v>
+        <v>8577.99</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>13166.36</v>
+        <v>13153.73</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>17150.37</v>
+        <v>17279.1</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>25801.16</v>
+        <v>25708.96</v>
       </c>
     </row>
     <row r="19">
@@ -1418,28 +1418,28 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>8512.959999999999</v>
+        <v>7740.21</v>
       </c>
       <c r="D19" s="13" t="n">
         <v>1084.8</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>1084.8</v>
+        <v>3517.53</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>4638.58</v>
+        <v>4751.43</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>13994.44</v>
+        <v>11248.54</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>20705.34</v>
+        <v>15452.79</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>24631.28</v>
+        <v>18538.5</v>
       </c>
     </row>
     <row r="20">
@@ -1449,28 +1449,28 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>9865.120000000001</v>
+        <v>10056.79</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>6077.84</v>
+        <v>6180.27</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>6553.81</v>
+        <v>6526.29</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>7207.85</v>
+        <v>7414.47</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>13429.88</v>
+        <v>13340.11</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>16865.96</v>
+        <v>16784.21</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>29209.22</v>
+        <v>31327.18</v>
       </c>
     </row>
     <row r="21">
@@ -1480,28 +1480,28 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>9580.540000000001</v>
+        <v>9398.110000000001</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>4147.14</v>
+        <v>4224.54</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>4736.06</v>
+        <v>4883.2</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>8227.360000000001</v>
+        <v>7006.97</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>12901.14</v>
+        <v>12183.78</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>16589.81</v>
+        <v>16282.53</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>26046.94</v>
+        <v>25913.48</v>
       </c>
     </row>
     <row r="22">
@@ -1511,28 +1511,28 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>10199.04</v>
+        <v>10098.74</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>4987.75</v>
+        <v>5257.78</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>8738.42</v>
+        <v>9391.57</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>14332.72</v>
+        <v>13499.63</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>17344.98</v>
+        <v>16530.54</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>30591.86</v>
+        <v>34388.92</v>
       </c>
     </row>
   </sheetData>
